--- a/icebreaker-workshop/stopwatch/power_measurements.xlsx
+++ b/icebreaker-workshop/stopwatch/power_measurements.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leegj\Documents\GitHub\GB3\GB3-RISC-V-Processor\icebreaker-workshop\stopwatch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cayma\Documents\GitHub\3GB3_proj\GB3-RISC-V-Processor\icebreaker-workshop\stopwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F25DC773A252ABDACC1048E2F9DC72D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2BC044-DBF6-4A15-AA61-D819395FB8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13680" yWindow="0" windowWidth="8003" windowHeight="12863" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="power" sheetId="1" r:id="rId1"/>
+    <sheet name="area" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,10 +25,227 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+  <si>
+    <t>POWER MEASUREMENTS</t>
+  </si>
+  <si>
+    <t>inv_baseline:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   0.35 w    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.08 A   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07 V </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2052 mWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    0.60 w    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.15 A  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2055 mWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2057 mWh</t>
+  </si>
+  <si>
+    <t>5.07 V</t>
+  </si>
+  <si>
+    <t>stopwatch - stopped:</t>
+  </si>
+  <si>
+    <t>stopwatch - active:</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Info: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">         ICESTORM_LC:       1/   5280     0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ICESTORM_RAM:       0/     30     0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               SB_IO:       2/     39     5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               SB_GB:       0/      8     0%</t>
+  </si>
+  <si>
+    <t>Info:    routing  7.69  7.69 Net LED1$SB_IO_OUT (16,0) -&gt; (18,31)</t>
+  </si>
+  <si>
+    <t>stopwatch:</t>
+  </si>
+  <si>
+    <t>Info: promoting CLK$SB_IO_IN (fanout 64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         ICESTORM_LC:     132/   5280     2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               SB_IO:      18/     39    46%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               SB_GB:       2/      8    25%</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #1, type ICESTORM_LC: wirelen solved = 227, spread = 435, legal = 487; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #1, type SB_GB: wirelen solved = 483, spread = 483, legal = 485; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #2, type ICESTORM_LC: wirelen solved = 226, spread = 442, legal = 494; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #2, type SB_GB: wirelen solved = 493, spread = 493, legal = 494; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #3, type ICESTORM_LC: wirelen solved = 244, spread = 446, legal = 484; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #3, type SB_GB: wirelen solved = 484, spread = 484, legal = 484; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #4, type ICESTORM_LC: wirelen solved = 250, spread = 461, legal = 468; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #4, type SB_GB: wirelen solved = 467, spread = 467, legal = 468; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #5, type ICESTORM_LC: wirelen solved = 254, spread = 445, legal = 482; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #5, type SB_GB: wirelen solved = 480, spread = 480, legal = 482; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #6, type ICESTORM_LC: wirelen solved = 283, spread = 466, legal = 499; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info:     at iteration #6, type SB_GB: wirelen solved = 496, spread = 496, legal = 499; time = 0.00s</t>
+  </si>
+  <si>
+    <t>Info: Max frequency for clock 'CLK$SB_IO_IN_$glb_clk': 53.70 MHz (PASS at 12.00 MHz)</t>
+  </si>
+  <si>
+    <t>Info: Max delay &lt;async&gt;                       -&gt; posedge CLK$SB_IO_IN_$glb_clk: 10.25 ns</t>
+  </si>
+  <si>
+    <t>Info: Max delay posedge CLK$SB_IO_IN_$glb_clk -&gt; &lt;async&gt;                      : 4.43 ns</t>
+  </si>
+  <si>
+    <t>Info: Critical path report for clock 'CLK$SB_IO_IN_$glb_clk' (posedge -&gt; posedge):</t>
+  </si>
+  <si>
+    <t>Info:                          Sink $nextpnr_ICESTORM_LC_4.I1</t>
+  </si>
+  <si>
+    <t>Info:      logic  0.68  3.83 Source $nextpnr_ICESTORM_LC_4.COUT</t>
+  </si>
+  <si>
+    <t>Info:    routing  0.00  3.83 Net $nextpnr_ICESTORM_LC_4$O (10,2) -&gt; (10,2)</t>
+  </si>
+  <si>
+    <t>Info:    routing  0.66  4.77 Net $nextpnr_ICESTORM_LC_5$I3 (10,2) -&gt; (10,2)</t>
+  </si>
+  <si>
+    <t>Info:                          Sink $nextpnr_ICESTORM_LC_5.I3</t>
+  </si>
+  <si>
+    <t>Info:      logic  0.87  5.64 Source $nextpnr_ICESTORM_LC_5.O</t>
+  </si>
+  <si>
+    <t>Info:                          Sink $nextpnr_ICESTORM_LC_6.I1</t>
+  </si>
+  <si>
+    <t>Info:      logic  0.68  8.08 Source $nextpnr_ICESTORM_LC_6.COUT</t>
+  </si>
+  <si>
+    <t>Info:    routing  0.00  8.08 Net $nextpnr_ICESTORM_LC_6$O (11,1) -&gt; (11,1)</t>
+  </si>
+  <si>
+    <t>Info:    routing  0.66  9.02 Net $nextpnr_ICESTORM_LC_7$I3 (11,1) -&gt; (11,1)</t>
+  </si>
+  <si>
+    <t>Info:                          Sink $nextpnr_ICESTORM_LC_7.I3</t>
+  </si>
+  <si>
+    <t>Info:      logic  0.87  9.89 Source $nextpnr_ICESTORM_LC_7.O</t>
+  </si>
+  <si>
+    <t>Info:                          Sink $nextpnr_ICESTORM_LC_8.I1</t>
+  </si>
+  <si>
+    <t>Info:      logic  0.68  12.33 Source $nextpnr_ICESTORM_LC_8.COUT</t>
+  </si>
+  <si>
+    <t>Info:    routing  0.00  12.33 Net $nextpnr_ICESTORM_LC_8$O (11,2) -&gt; (11,2)</t>
+  </si>
+  <si>
+    <t>Info:    routing  0.66  13.27 Net $nextpnr_ICESTORM_LC_9$I3 (11,2) -&gt; (11,2)</t>
+  </si>
+  <si>
+    <t>Info:                          Sink $nextpnr_ICESTORM_LC_9.I3</t>
+  </si>
+  <si>
+    <t>Info:      logic  0.87  14.14 Source $nextpnr_ICESTORM_LC_9.O</t>
+  </si>
+  <si>
+    <t>Info:    routing  2.95  2.95 Net BTN_N$SB_IO_IN (16,0) -&gt; (17,3)</t>
+  </si>
+  <si>
+    <t>Info:    routing  6.84  10.67 Net LED4$SB_IO_OUT (17,3) -&gt; (19,31)</t>
+  </si>
+  <si>
+    <t>Info: Critical path report for cross-domain path '&lt;async&gt;' -&gt; 'posedge CLK$SB_IO_IN_$glb_clk':</t>
+  </si>
+  <si>
+    <t>Info:    routing  4.14  4.14 Net BTN2$SB_IO_IN (21,0) -&gt; (12,2)</t>
+  </si>
+  <si>
+    <t>Info: Critical path report for cross-domain path 'posedge CLK$SB_IO_IN_$glb_clk' -&gt; '&lt;async&gt;':</t>
+  </si>
+  <si>
+    <t>Info:    routing  3.49  4.89 Net P1A10$SB_IO_OUT (10,1) -&gt; (6,0)</t>
+  </si>
+  <si>
+    <t>Info: Max frequency for clock 'CLK$SB_IO_IN_$glb_clk': 59.79 MHz (PASS at 12.00 MHz)</t>
+  </si>
+  <si>
+    <t>Info: Max delay &lt;async&gt;                       -&gt; posedge CLK$SB_IO_IN_$glb_clk: 11.44 ns</t>
+  </si>
+  <si>
+    <t>Info: Max delay posedge CLK$SB_IO_IN_$glb_clk -&gt; &lt;async&gt;                      : 4.89 ns</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -55,8 +273,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,9 +556,387 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C032E41C-D97E-48E2-97F1-CB3AC73DFE77}">
+  <dimension ref="A1:B58"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/icebreaker-workshop/stopwatch/power_measurements.xlsx
+++ b/icebreaker-workshop/stopwatch/power_measurements.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cayma\Documents\GitHub\3GB3_proj\GB3-RISC-V-Processor\icebreaker-workshop\stopwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2BC044-DBF6-4A15-AA61-D819395FB8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1872B67A-66B9-4864-8015-75DAD8DF9179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13680" yWindow="0" windowWidth="8003" windowHeight="12863" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="3472" windowWidth="16200" windowHeight="9308" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="power" sheetId="1" r:id="rId1"/>
     <sheet name="area" sheetId="2" r:id="rId2"/>
+    <sheet name="picoscope" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,6 +24,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -291,6 +314,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -939,4 +1026,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DB3C09-3E03-439B-8C18-5AB9730E4350}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="97.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="321" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/icebreaker-workshop/stopwatch/power_measurements.xlsx
+++ b/icebreaker-workshop/stopwatch/power_measurements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cayma\Documents\GitHub\3GB3_proj\GB3-RISC-V-Processor\icebreaker-workshop\stopwatch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leegj\Documents\GitHub\GB3\GB3-RISC-V-Processor\icebreaker-workshop\stopwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1872B67A-66B9-4864-8015-75DAD8DF9179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C279EE8E-ABA7-4AF1-9585-450602F130CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="3472" windowWidth="16200" windowHeight="9308" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="power" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="97">
   <si>
     <t>POWER MEASUREMENTS</t>
   </si>
@@ -90,9 +90,6 @@
     <t>stopwatch - active:</t>
   </si>
   <si>
-    <t>area</t>
-  </si>
-  <si>
     <t xml:space="preserve">Info: </t>
   </si>
   <si>
@@ -253,6 +250,96 @@
   </si>
   <si>
     <t>Info: Max delay posedge CLK$SB_IO_IN_$glb_clk -&gt; &lt;async&gt;                      : 4.89 ns</t>
+  </si>
+  <si>
+    <t>Raw Log</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>inv_baseline</t>
+  </si>
+  <si>
+    <t>inv_baseline Total</t>
+  </si>
+  <si>
+    <t>inv_baseline %</t>
+  </si>
+  <si>
+    <t>stopwatch</t>
+  </si>
+  <si>
+    <t>stopwatch Total</t>
+  </si>
+  <si>
+    <t>stopwatch %</t>
+  </si>
+  <si>
+    <t>ICESTORM_LC</t>
+  </si>
+  <si>
+    <t>ICESTORM_RAM</t>
+  </si>
+  <si>
+    <t>SB_IO</t>
+  </si>
+  <si>
+    <t>SB_GB</t>
+  </si>
+  <si>
+    <t>Timing (stopwatch only)</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Max frequency (run 1)</t>
+  </si>
+  <si>
+    <t>53.70 MHz</t>
+  </si>
+  <si>
+    <t>Max frequency (run 2)</t>
+  </si>
+  <si>
+    <t>59.79 MHz</t>
+  </si>
+  <si>
+    <t>Clock constraint</t>
+  </si>
+  <si>
+    <t>12.00 MHz</t>
+  </si>
+  <si>
+    <t>Timing result</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Max delay async → clk</t>
+  </si>
+  <si>
+    <t>10.25 ns</t>
+  </si>
+  <si>
+    <t>Max delay clk → async</t>
+  </si>
+  <si>
+    <t>4.43 ns</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>1 Hz Square Wave — PicoScope 2204A Measurement</t>
+  </si>
+  <si>
+    <t>Frequency: 1 Hz | Period: 1 s | High: ~3.3 V | Low: 0 V | Waveform: Square</t>
   </si>
 </sst>
 </file>
@@ -296,9 +383,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -716,311 +815,498 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C032E41C-D97E-48E2-97F1-CB3AC73DFE77}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="8.86328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5280</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>132</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5280</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>30</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>39</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="3">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3">
+        <v>39</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>8</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1030,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DB3C09-3E03-439B-8C18-5AB9730E4350}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="97.73046875" customWidth="1"/>
@@ -1041,6 +1327,16 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
